--- a/public_administration_forms/011_public_policy_opinion_survey--public_administration_forms.xlsx
+++ b/public_administration_forms/011_public_policy_opinion_survey--public_administration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'employed',_'label':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'employed', 'label': 'Employed'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'retired',_'label':_'retired'}</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'retired', 'label': 'Retired'}</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'unemployed',_'label':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'unemployed', 'label': 'Unemployed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'democratic-party',_'label':_'democratic_party'}</t>
+          <t>democratic_party</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'democratic-party', 'label': 'Democratic Party'}</t>
+          <t>Democratic Party</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'republican-party',_'label':_'republican_party'}</t>
+          <t>republican_party</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'republican-party', 'label': 'Republican Party'}</t>
+          <t>Republican Party</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'independent',_'label':_'independent'}</t>
+          <t>independent</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'independent', 'label': 'Independent'}</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'high-school',_'label':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'high-school', 'label': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'some-college',_'label':_'some_college'}</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'some-college', 'label': 'Some College'}</t>
+          <t>Some College</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'college',_'label':_'college'}</t>
+          <t>college</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'college', 'label': 'College'}</t>
+          <t>College</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'government',_'label':_'government'}</t>
+          <t>government</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'government', 'label': 'Government'}</t>
+          <t>Government</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'private',_'label':_'private'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'private', 'label': 'Private'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'non-profit',_'label':_'non-profit'}</t>
+          <t>non-profit</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'non-profit', 'label': 'Non-profit'}</t>
+          <t>Non-profit</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'daily',_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'daily', 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'weekly',_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'weekly', 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'monthly',_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'monthly', 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'rarely',_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'rarely', 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'never',_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'never', 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'own',_'label':_'own'}</t>
+          <t>own</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'own', 'label': 'Own'}</t>
+          <t>Own</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'rent',_'label':_'rent'}</t>
+          <t>rent</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'rent', 'label': 'Rent'}</t>
+          <t>Rent</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'daily',_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'daily', 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'weekly',_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'weekly', 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'monthly',_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'monthly', 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'rarely',_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'rarely', 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'never',_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'never', 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
